--- a/Team-Data/2007-08/2-28-2007-08.xlsx
+++ b/Team-Data/2007-08/2-28-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -769,7 +836,7 @@
         <v>29</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -793,7 +860,7 @@
         <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -945,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1136,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="n">
         <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.655</v>
+        <v>0.667</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.462</v>
@@ -1598,28 +1665,28 @@
         <v>5.8</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S7" t="n">
         <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U7" t="n">
         <v>20.1</v>
@@ -1637,25 +1704,25 @@
         <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
         <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="n">
         <v>6</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>7</v>
       </c>
       <c r="AG7" t="n">
         <v>7</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -1679,13 +1746,13 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1697,16 +1764,16 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1724,7 +1791,7 @@
         <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2231,10 +2298,10 @@
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>8</v>
@@ -2452,7 +2519,7 @@
         <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2565,10 +2632,10 @@
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2580,7 +2647,7 @@
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
@@ -2762,7 +2829,7 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -2816,7 +2883,7 @@
         <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.707</v>
+        <v>0.702</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2878,22 +2945,22 @@
         <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P14" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
         <v>10.6</v>
       </c>
       <c r="S14" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2905,25 +2972,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>9</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3126,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
         <v>7</v>
@@ -3153,7 +3220,7 @@
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>0.179</v>
+        <v>0.182</v>
       </c>
       <c r="H16" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I16" t="n">
         <v>35.3</v>
       </c>
       <c r="J16" t="n">
-        <v>77.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
         <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
         <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R16" t="n">
         <v>9.199999999999999</v>
@@ -3260,10 +3327,10 @@
         <v>38.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>7.4</v>
@@ -3272,7 +3339,7 @@
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z16" t="n">
         <v>20.5</v>
@@ -3281,13 +3348,13 @@
         <v>21.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.3</v>
+        <v>-7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3302,13 +3369,13 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,10 +3384,10 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
@@ -3347,22 +3414,22 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -3391,58 +3458,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
         <v>80.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
         <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
         <v>14.7</v>
@@ -3460,16 +3527,16 @@
         <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
@@ -3481,10 +3548,10 @@
         <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -3499,7 +3566,7 @@
         <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -3508,7 +3575,7 @@
         <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR17" t="n">
         <v>11</v>
@@ -3538,10 +3605,10 @@
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -3755,37 +3822,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.448</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J19" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>5.9</v>
       </c>
       <c r="M19" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
         <v>20.2</v>
@@ -3794,22 +3861,22 @@
         <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S19" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T19" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U19" t="n">
         <v>23.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W19" t="n">
         <v>6.4</v>
@@ -3827,25 +3894,25 @@
         <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.6</v>
+        <v>-4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,7 +3921,7 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
         <v>19</v>
@@ -3869,7 +3936,7 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>24</v>
@@ -3881,13 +3948,13 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3908,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4085,7 @@
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4027,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4221,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
@@ -4266,10 +4333,10 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4497,7 @@
         <v>14</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4679,7 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4879,7 @@
         <v>5</v>
       </c>
       <c r="BA24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
@@ -5143,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5229,7 +5296,7 @@
         <v>35.8</v>
       </c>
       <c r="J27" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.458</v>
@@ -5238,7 +5305,7 @@
         <v>7.9</v>
       </c>
       <c r="M27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N27" t="n">
         <v>0.378</v>
@@ -5256,16 +5323,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T27" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U27" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V27" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W27" t="n">
         <v>6.6</v>
@@ -5283,16 +5350,16 @@
         <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
@@ -5301,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5337,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5516,7 +5583,7 @@
         <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT28" t="n">
         <v>1</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6047,7 +6114,7 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-28-2007-08</t>
+          <t>2008-02-28</t>
         </is>
       </c>
     </row>
